--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
@@ -911,22 +911,22 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.945945945945</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.452991452991</v>
+        <v>-91.570881226053</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H17" s="15">
-        <v>-53.333333333333</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K17" s="15">
-        <v>-46.774193548387</v>
+        <v>-45.205479452054</v>
       </c>
       <c r="L17" s="15">
-        <v>-28.260869565217</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M17" s="15">
-        <v>13.793103448275</v>
+        <v>29.032258064516</v>
       </c>
       <c r="N17" s="15">
-        <v>-62.5</v>
+        <v>-60.396039603960</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.411764705882</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L18" s="15">
-        <v>-52</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="M18" s="15">
-        <v>-83.333333333333</v>
+        <v>-83.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.256916996047</v>
+        <v>-95.517241379310</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-13.636363636363</v>
+        <v>-6.25</v>
       </c>
       <c r="F19" s="14">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>5.797101449275</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="I19" s="14">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="J19" s="14">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>13.684210526315</v>
+        <v>9.909909909909</v>
       </c>
       <c r="L19" s="15">
-        <v>31.707317073170</v>
+        <v>15.094339622641</v>
       </c>
       <c r="M19" s="15">
-        <v>66.153846153846</v>
+        <v>62.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.6</v>
+        <v>-18.120805369127</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>20</v>
+      </c>
+      <c r="G20" s="14">
+        <v>16</v>
+      </c>
+      <c r="H20" s="15">
+        <v>25</v>
+      </c>
+      <c r="I20" s="14">
+        <v>27</v>
+      </c>
+      <c r="J20" s="14">
+        <v>30</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-10</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-25</v>
+      </c>
+      <c r="M20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>16</v>
-      </c>
-      <c r="G20" s="14">
-        <v>20</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I20" s="14">
-        <v>22</v>
-      </c>
-      <c r="J20" s="14">
-        <v>26</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-15.384615384615</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-29.032258064516</v>
-      </c>
-      <c r="M20" s="15">
-        <v>-15.384615384615</v>
-      </c>
       <c r="N20" s="15">
-        <v>-93.854748603352</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.463414634146</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="I21" s="17">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="J21" s="17">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.777777777777</v>
+        <v>-11.742424242424</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.791469194312</v>
+        <v>-15.272727272727</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.875536480686</v>
+        <v>-10.727969348659</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.992509363295</v>
+        <v>-81.285140562249</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
         <v>33.333333333333</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
         <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-18.75</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>23.076923076923</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>6.666666666666</v>
+        <v>5.263157894736</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.809523809523</v>
+        <v>17.5</v>
       </c>
       <c r="F24" s="14">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G24" s="14">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.407407407407</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I24" s="14">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="J24" s="14">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.319502074688</v>
+        <v>-0.355871886120</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.508196721311</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M24" s="15">
-        <v>59.589041095890</v>
+        <v>71.779141104294</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D25" s="14">
         <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-52.631578947368</v>
+        <v>26.315789473684</v>
       </c>
       <c r="F25" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G25" s="14">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.083333333333</v>
+        <v>-18.478260869565</v>
       </c>
       <c r="I25" s="14">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.545454545454</v>
+        <v>-22.516556291390</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.512820512820</v>
+        <v>-17.605633802816</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>72.727272727272</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.859154929577</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J26" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.075268817204</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="L26" s="15">
-        <v>3.370786516853</v>
+        <v>-6.306306306306</v>
       </c>
       <c r="M26" s="15">
-        <v>3.370786516853</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,13 +1476,13 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,13 +1517,13 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
         <v>-80</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,10 +905,10 @@
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -920,7 +920,7 @@
         <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>166.666666666667</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>166.666666666667</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.347826086956</v>
+        <v>3.846153846153</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.294117647058</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-41.304347826087</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.570881226053</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-27.272727272727</v>
+        <v>-18.75</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
         <v>47</v>
       </c>
       <c r="H17" s="15">
-        <v>-48.936170212766</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>-45.205479452054</v>
+        <v>-38.202247191011</v>
       </c>
       <c r="L17" s="15">
-        <v>-38.461538461538</v>
+        <v>-38.202247191011</v>
       </c>
       <c r="M17" s="15">
-        <v>29.032258064516</v>
+        <v>48.648648648648</v>
       </c>
       <c r="N17" s="15">
-        <v>-60.396039603960</v>
+        <v>-51.327433628318</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
         <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.909090909090</v>
+        <v>-36</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.064516129032</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="M18" s="15">
-        <v>-83.75</v>
+        <v>-82.608695652173</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.517241379310</v>
+        <v>-95.076923076923</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
         <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.470588235294</v>
+        <v>-13.698630136986</v>
       </c>
       <c r="I19" s="14">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
-        <v>9.909909909909</v>
+        <v>8.661417322834</v>
       </c>
       <c r="L19" s="15">
-        <v>15.094339622641</v>
+        <v>7.8125</v>
       </c>
       <c r="M19" s="15">
-        <v>62.666666666666</v>
+        <v>64.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.120805369127</v>
+        <v>-16.867469879518</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-10</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.75</v>
+        <v>-93.920335429769</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
         <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G21" s="17">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.049382716049</v>
+        <v>-12.883435582822</v>
       </c>
       <c r="I21" s="17">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="J21" s="17">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.742424242424</v>
+        <v>-9.570957095709</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.272727272727</v>
+        <v>-20.809248554913</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.727969348659</v>
+        <v>-7.118644067796</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.285140562249</v>
+        <v>-80.287769784172</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
+        <v>200</v>
+      </c>
+      <c r="M22" s="15">
         <v>100</v>
-      </c>
-      <c r="M22" s="15">
-        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
         <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.75</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K23" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="L23" s="15">
-        <v>11.111111111111</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M23" s="15">
-        <v>5.263157894736</v>
+        <v>4.545454545454</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>17.5</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="F24" s="14">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G24" s="14">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.157894736842</v>
+        <v>-14.689265536723</v>
       </c>
       <c r="I24" s="14">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="J24" s="14">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.355871886120</v>
+        <v>-2.160493827160</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.761904761904</v>
+        <v>-5.373134328358</v>
       </c>
       <c r="M24" s="15">
-        <v>71.779141104294</v>
+        <v>80.113636363636</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E25" s="15">
-        <v>26.315789473684</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G25" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.478260869565</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="J25" s="14">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.516556291390</v>
+        <v>-26.881720430107</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.605633802816</v>
+        <v>-13.924050632911</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>3.225806451612</v>
+        <v>1.639344262295</v>
       </c>
       <c r="I26" s="14">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.886792452830</v>
+        <v>-6.4</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.306306306306</v>
+        <v>-10</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>-4.098360655737</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>80</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>2</v>
+      </c>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
         <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="15">
         <v>-50</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>6</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
         <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>3.846153846153</v>
+        <v>26.923076923076</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.714285714285</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.304347826087</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.909090909090</v>
+        <v>-90.265486725663</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.75</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.404255319148</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="K17" s="15">
-        <v>-38.202247191011</v>
+        <v>-34.951456310679</v>
       </c>
       <c r="L17" s="15">
-        <v>-38.202247191011</v>
+        <v>-33</v>
       </c>
       <c r="M17" s="15">
-        <v>48.648648648648</v>
+        <v>67.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.327433628318</v>
+        <v>-48.062015503876</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-36</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.974358974359</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.608695652173</v>
+        <v>-83.505154639175</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.076923076923</v>
+        <v>-95.616438356164</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.698630136986</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="I19" s="14">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J19" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>8.661417322834</v>
+        <v>8.633093525179</v>
       </c>
       <c r="L19" s="15">
-        <v>7.8125</v>
+        <v>-2.580645161290</v>
       </c>
       <c r="M19" s="15">
-        <v>64.285714285714</v>
+        <v>67.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>-16.867469879518</v>
+        <v>-18.817204301075</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>16.666666666666</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.451612903225</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.952380952381</v>
+        <v>-30</v>
       </c>
       <c r="M20" s="15">
-        <v>-6.451612903225</v>
+        <v>6.060606060606</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.920335429769</v>
+        <v>-93.421052631578</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
         <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="F21" s="17">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="G21" s="17">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.883435582822</v>
+        <v>-4.938271604938</v>
       </c>
       <c r="I21" s="17">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="J21" s="17">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.570957095709</v>
+        <v>-9.356725146198</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.809248554913</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.118644067796</v>
+        <v>-2.821316614420</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.287769784172</v>
+        <v>-80.179028132992</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I22" s="14">
+        <v>8</v>
+      </c>
+      <c r="J22" s="14">
         <v>6</v>
       </c>
-      <c r="J22" s="14">
-        <v>5</v>
-      </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>-45.833333333333</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.837837837837</v>
+        <v>-34.210526315789</v>
       </c>
       <c r="L23" s="15">
-        <v>-25.806451612903</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="M23" s="15">
-        <v>4.545454545454</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.953488372093</v>
+        <v>-41.304347826087</v>
       </c>
       <c r="F24" s="14">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G24" s="14">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.689265536723</v>
+        <v>-15.204678362573</v>
       </c>
       <c r="I24" s="14">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="J24" s="14">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.160493827160</v>
+        <v>-6.486486486486</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.373134328358</v>
+        <v>-8.465608465608</v>
       </c>
       <c r="M24" s="15">
-        <v>80.113636363636</v>
+        <v>78.350515463917</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.714285714285</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F25" s="14">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G25" s="14">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-43</v>
       </c>
       <c r="I25" s="14">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J25" s="14">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.881720430107</v>
+        <v>-33.802816901408</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.924050632911</v>
+        <v>-22.099447513812</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-31.578947368421</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>1.639344262295</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="14">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J26" s="14">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.4</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L26" s="15">
-        <v>-10</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.098360655737</v>
+        <v>-7.246376811594</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
@@ -1447,13 +1447,13 @@
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
         <v>2</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="14">
-        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="L29" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
         <v>2</v>
-      </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>4</v>
       </c>
       <c r="H30" s="15">
         <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="L30" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -882,51 +882,51 @@
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>90</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>26.923076923076</v>
+        <v>29.629629629629</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.735849056603</v>
+        <v>-40.677966101694</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.888888888888</v>
+        <v>-39.655172413793</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.265486725663</v>
+        <v>-90.514905149051</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-7.142857142857</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="14">
         <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.204081632653</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.951456310679</v>
+        <v>-32.456140350877</v>
       </c>
       <c r="L17" s="15">
-        <v>-33</v>
+        <v>-30.630630630630</v>
       </c>
       <c r="M17" s="15">
-        <v>67.5</v>
+        <v>71.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.062015503876</v>
+        <v>-47.260273972602</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
         <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-65.217391304347</v>
+        <v>-64.583333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-83.505154639175</v>
+        <v>-85.087719298245</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.616438356164</v>
+        <v>-95.812807881773</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.060606060606</v>
+        <v>4.918032786885</v>
       </c>
       <c r="I19" s="14">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="K19" s="15">
-        <v>8.633093525179</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.580645161290</v>
+        <v>-1.149425287356</v>
       </c>
       <c r="M19" s="15">
-        <v>67.777777777777</v>
+        <v>68.627450980392</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.817204301075</v>
+        <v>-17.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>16</v>
+      </c>
+      <c r="G20" s="14">
+        <v>15</v>
+      </c>
+      <c r="H20" s="15">
+        <v>6.666666666666</v>
+      </c>
+      <c r="I20" s="14">
+        <v>37</v>
+      </c>
+      <c r="J20" s="14">
+        <v>41</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-9.756097560975</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-31.481481481481</v>
+      </c>
+      <c r="M20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>19</v>
-      </c>
-      <c r="G20" s="14">
-        <v>17</v>
-      </c>
-      <c r="H20" s="15">
-        <v>11.764705882352</v>
-      </c>
-      <c r="I20" s="14">
-        <v>35</v>
-      </c>
-      <c r="J20" s="14">
-        <v>37</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-5.405405405405</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-30</v>
-      </c>
-      <c r="M20" s="15">
-        <v>6.060606060606</v>
-      </c>
       <c r="N20" s="15">
-        <v>-93.421052631578</v>
+        <v>-93.686006825938</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.564102564102</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.938271604938</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I21" s="17">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="J21" s="17">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.356725146198</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.390243902439</v>
+        <v>-23.178807947019</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.821316614420</v>
+        <v>-4.132231404958</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.179028132992</v>
+        <v>-79.861111111111</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M22" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>-34.210526315789</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L23" s="15">
-        <v>-32.432432432432</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>-3.846153846153</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D24" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.304347826087</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="G24" s="14">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.204678362573</v>
+        <v>-9.189189189189</v>
       </c>
       <c r="I24" s="14">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="J24" s="14">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.486486486486</v>
+        <v>-6.103286384976</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.465608465608</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M24" s="15">
-        <v>78.350515463917</v>
+        <v>85.185185185185</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-77.777777777777</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="F25" s="14">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G25" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H25" s="15">
-        <v>-43</v>
+        <v>-40.178571428571</v>
       </c>
       <c r="I25" s="14">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="J25" s="14">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.802816901408</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.099447513812</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.448275862068</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="I26" s="14">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.571428571428</v>
+        <v>-11.801242236024</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.328767123287</v>
+        <v>-8.974358974358</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.246376811594</v>
+        <v>-11.801242236024</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
+        <v>15</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L28" s="15">
         <v>0</v>
-      </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>50</v>
-      </c>
-      <c r="I28" s="14">
-        <v>9</v>
-      </c>
-      <c r="J28" s="14">
-        <v>13</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-30.769230769230</v>
-      </c>
-      <c r="L28" s="15">
-        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,7 +1494,7 @@
         <v>-40</v>
       </c>
       <c r="L29" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>-40</v>
       </c>
       <c r="L30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -905,28 +905,28 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>14.285714285714</v>
+        <v>-10</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>114.285714285714</v>
+        <v>77.777777777777</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>29.629629629629</v>
+        <v>18.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.677966101694</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.655172413793</v>
+        <v>-39.682539682539</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.514905149051</v>
+        <v>-90.594059405940</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-27.272727272727</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F17" s="14">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.384615384615</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="I17" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K17" s="15">
-        <v>-32.456140350877</v>
+        <v>-35.433070866141</v>
       </c>
       <c r="L17" s="15">
-        <v>-30.630630630630</v>
+        <v>-31.092436974789</v>
       </c>
       <c r="M17" s="15">
-        <v>71.111111111111</v>
+        <v>67.346938775510</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.260273972602</v>
+        <v>-46.753246753246</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-70.588235294117</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-42.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-64.583333333333</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-85.087719298245</v>
+        <v>-81.147540983606</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.812807881773</v>
+        <v>-94.796380090497</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>23.529411764705</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>4.918032786885</v>
+        <v>26.785714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="J19" s="14">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K19" s="15">
-        <v>10.256410256410</v>
+        <v>16.766467065868</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.149425287356</v>
+        <v>3.174603174603</v>
       </c>
       <c r="M19" s="15">
-        <v>68.627450980392</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-17.307692307692</v>
+        <v>-12.556053811659</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
         <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.756097560975</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.481481481481</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.686006825938</v>
+        <v>-93.053311793214</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>4.878048780487</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G21" s="17">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.921568627450</v>
+        <v>-0.645161290322</v>
       </c>
       <c r="I21" s="17">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="J21" s="17">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.936507936507</v>
+        <v>-6.443914081145</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.178807947019</v>
+        <v>-20.325203252032</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.132231404958</v>
+        <v>-2.487562189054</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.861111111111</v>
+        <v>-78.902045209903</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="14">
+        <v>10</v>
+      </c>
+      <c r="J22" s="14">
+        <v>8</v>
+      </c>
+      <c r="K22" s="15">
         <v>25</v>
       </c>
-      <c r="I22" s="14">
-        <v>9</v>
-      </c>
-      <c r="J22" s="14">
-        <v>7</v>
-      </c>
-      <c r="K22" s="15">
-        <v>28.571428571428</v>
-      </c>
       <c r="L22" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-26.315789473684</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.232558139534</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M23" s="15">
-        <v>11.111111111111</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G24" s="14">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.189189189189</v>
+        <v>-14.210526315789</v>
       </c>
       <c r="I24" s="14">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="J24" s="14">
-        <v>426</v>
+        <v>471</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.103286384976</v>
+        <v>-6.157112526539</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.761904761904</v>
+        <v>-4.121475054229</v>
       </c>
       <c r="M24" s="15">
-        <v>85.185185185185</v>
+        <v>83.402489626556</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.709677419354</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G25" s="14">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.178571428571</v>
+        <v>-52.991452991453</v>
       </c>
       <c r="I25" s="14">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J25" s="14">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.426229508196</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.568627450980</v>
+        <v>-25.217391304347</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-28.571428571428</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.470588235294</v>
+        <v>-19.696969696969</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.801242236024</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.974358974358</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.801242236024</v>
+        <v>-10.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>11.111111111111</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -882,24 +882,24 @@
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -923,10 +923,10 @@
         <v>-10</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>16</v>
@@ -952,22 +952,22 @@
         <v>77.777777777777</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>18.75</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.424242424242</v>
+        <v>-41.891891891891</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.682539682539</v>
+        <v>-34.848484848484</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.594059405940</v>
+        <v>-90.046296296296</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-61.538461538461</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.629629629629</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K17" s="15">
-        <v>-35.433070866141</v>
+        <v>-33.088235294117</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.092436974789</v>
+        <v>-30.534351145038</v>
       </c>
       <c r="M17" s="15">
-        <v>67.346938775510</v>
+        <v>65.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.753246753246</v>
+        <v>-44.848484848484</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.5</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L18" s="15">
-        <v>-52.083333333333</v>
+        <v>-50.943396226415</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.147540983606</v>
+        <v>-80.882352941176</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.796380090497</v>
+        <v>-94.491525423728</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G19" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>26.785714285714</v>
+        <v>28.301886792452</v>
       </c>
       <c r="I19" s="14">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="J19" s="14">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K19" s="15">
-        <v>16.766467065868</v>
+        <v>15.555555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>3.174603174603</v>
+        <v>-0.952380952380</v>
       </c>
       <c r="M19" s="15">
-        <v>66.666666666666</v>
+        <v>56.390977443609</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.556053811659</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.521739130434</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.333333333333</v>
+        <v>-26.865671641791</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.272727272727</v>
+        <v>6.521739130434</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.053311793214</v>
+        <v>-92.530487804878</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>4.878048780487</v>
+        <v>18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G21" s="17">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H21" s="18">
-        <v>-0.645161290322</v>
+        <v>3.378378378378</v>
       </c>
       <c r="I21" s="17">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="J21" s="17">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.443914081145</v>
+        <v>-5.099778270509</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.325203252032</v>
+        <v>-21.467889908256</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.487562189054</v>
+        <v>-3.820224719101</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.902045209903</v>
+        <v>-78.524836929252</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="15">
         <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>6</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L22" s="15">
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.777777777777</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K23" s="15">
-        <v>-26.086956521739</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="L23" s="15">
-        <v>-19.047619047619</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="M23" s="15">
-        <v>21.428571428571</v>
+        <v>36.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D24" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.111111111111</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="G24" s="14">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.210526315789</v>
+        <v>-3.465346534653</v>
       </c>
       <c r="I24" s="14">
-        <v>442</v>
+        <v>512</v>
       </c>
       <c r="J24" s="14">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.157112526539</v>
+        <v>-2.661596958174</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.121475054229</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M24" s="15">
-        <v>83.402489626556</v>
+        <v>83.512544802867</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>34.482758620689</v>
       </c>
       <c r="F25" s="14">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="G25" s="14">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H25" s="15">
-        <v>-52.991452991453</v>
+        <v>-31.531531531531</v>
       </c>
       <c r="I25" s="14">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="J25" s="14">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.820895522388</v>
+        <v>-28.956228956229</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.217391304347</v>
+        <v>-16.600790513834</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>18.181818181818</v>
+        <v>56.25</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.696969696969</v>
+        <v>3.174603174603</v>
       </c>
       <c r="I26" s="14">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="J26" s="14">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.302325581395</v>
+        <v>-2.659574468085</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.864406779661</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.857142857142</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-23.529411764705</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-50</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-50</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -854,35 +854,35 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
         <v>-71.428571428571</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I15" s="14">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
+        <v>9</v>
+      </c>
+      <c r="K15" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="14">
-        <v>9</v>
-      </c>
-      <c r="J15" s="14">
-        <v>7</v>
-      </c>
-      <c r="K15" s="15">
-        <v>28.571428571428</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-10</v>
-      </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>77.777777777777</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>22.857142857142</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.891891891891</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.848484848484</v>
+        <v>-40.789473684210</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.046296296296</v>
+        <v>-90.343347639485</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>11.111111111111</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.404255319148</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J17" s="14">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.088235294117</v>
+        <v>-24.460431654676</v>
       </c>
       <c r="L17" s="15">
-        <v>-30.534351145038</v>
+        <v>-26.056338028169</v>
       </c>
       <c r="M17" s="15">
-        <v>65.454545454545</v>
+        <v>81.034482758620</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.848484848484</v>
+        <v>-42.307692307692</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.176470588235</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.095238095238</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="L18" s="15">
-        <v>-50.943396226415</v>
+        <v>-48.214285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.882352941176</v>
+        <v>-79.432624113475</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.491525423728</v>
+        <v>-94.280078895463</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F19" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>28.301886792452</v>
+        <v>21.311475409836</v>
       </c>
       <c r="I19" s="14">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="J19" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K19" s="15">
-        <v>15.555555555555</v>
+        <v>13.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.952380952380</v>
+        <v>-2.991452991452</v>
       </c>
       <c r="M19" s="15">
-        <v>56.390977443609</v>
+        <v>53.378378378378</v>
       </c>
       <c r="N19" s="15">
-        <v>-16.8</v>
+        <v>-17.153284671532</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.921568627450</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.865671641791</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="M20" s="15">
-        <v>6.521739130434</v>
+        <v>8</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.530487804878</v>
+        <v>-92.394366197183</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>18.75</v>
+        <v>16.216216216216</v>
       </c>
       <c r="F21" s="17">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G21" s="17">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H21" s="18">
-        <v>3.378378378378</v>
+        <v>8.219178082191</v>
       </c>
       <c r="I21" s="17">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="J21" s="17">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.099778270509</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.467889908256</v>
+        <v>-20.538720538720</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.820224719101</v>
+        <v>-2.277432712215</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.524836929252</v>
+        <v>-78.117756142790</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>42.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
+        <v>200</v>
+      </c>
+      <c r="F23" s="14">
         <v>20</v>
       </c>
-      <c r="F23" s="14">
-        <v>17</v>
-      </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>21.428571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J23" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.607843137254</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.888888888888</v>
+        <v>-8</v>
       </c>
       <c r="M23" s="15">
-        <v>36.666666666666</v>
+        <v>27.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D24" s="14">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>18.181818181818</v>
+        <v>23.684210526315</v>
       </c>
       <c r="F24" s="14">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="G24" s="14">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.465346534653</v>
+        <v>10.824742268041</v>
       </c>
       <c r="I24" s="14">
-        <v>512</v>
+        <v>559</v>
       </c>
       <c r="J24" s="14">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.661596958174</v>
+        <v>-0.886524822695</v>
       </c>
       <c r="L24" s="15">
-        <v>3.225806451612</v>
+        <v>1.636363636363</v>
       </c>
       <c r="M24" s="15">
-        <v>83.512544802867</v>
+        <v>71.472392638036</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>34.482758620689</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="G25" s="14">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.531531531531</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="I25" s="14">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="J25" s="14">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.956228956229</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.600790513834</v>
+        <v>-18.661971830985</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
         <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>56.25</v>
+        <v>43.75</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>3.174603174603</v>
+        <v>21.875</v>
       </c>
       <c r="I26" s="14">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="J26" s="14">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.659574468085</v>
+        <v>0.980392156862</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.955223880597</v>
+        <v>-5.069124423963</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.575757575757</v>
+        <v>-1.904761904761</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>13</v>
+      </c>
+      <c r="J27" s="14">
         <v>11</v>
       </c>
-      <c r="J27" s="14">
-        <v>9</v>
-      </c>
       <c r="K27" s="15">
-        <v>22.222222222222</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L27" s="15">
-        <v>-26.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-22.222222222222</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
         <v>-66.666666666666</v>
@@ -1538,7 +1538,7 @@
         <v>50</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
         <v>-66.666666666666</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -905,28 +905,28 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="14">
+        <v>11</v>
+      </c>
+      <c r="J15" s="14">
+        <v>11</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
         <v>10</v>
       </c>
-      <c r="J15" s="14">
-        <v>9</v>
-      </c>
-      <c r="K15" s="15">
-        <v>11.111111111111</v>
-      </c>
-      <c r="L15" s="15">
+      <c r="M15" s="15">
+        <v>83.333333333333</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>12.5</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-38.75</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.789473684210</v>
+        <v>-37.974683544303</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.343347639485</v>
+        <v>-90.4296875</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>333.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="I17" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J17" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K17" s="15">
-        <v>-24.460431654676</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.056338028169</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="M17" s="15">
-        <v>81.034482758620</v>
+        <v>90</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.307692307692</v>
+        <v>-41.237113402061</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>8</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>18.181818181818</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-32.558139534883</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.214285714285</v>
+        <v>-38.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.432624113475</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.280078895463</v>
+        <v>-93.084112149532</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>18</v>
+      </c>
+      <c r="D19" s="14">
         <v>19</v>
       </c>
-      <c r="D19" s="14">
-        <v>20</v>
-      </c>
       <c r="E19" s="15">
-        <v>-5</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F19" s="14">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>21.311475409836</v>
+        <v>6.349206349206</v>
       </c>
       <c r="I19" s="14">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="J19" s="14">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="K19" s="15">
-        <v>13.5</v>
+        <v>10.502283105022</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.991452991452</v>
+        <v>-4.724409448818</v>
       </c>
       <c r="M19" s="15">
-        <v>53.378378378378</v>
+        <v>52.201257861635</v>
       </c>
       <c r="N19" s="15">
-        <v>-17.153284671532</v>
+        <v>-18.518518518518</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>13.636363636363</v>
       </c>
       <c r="I20" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.571428571428</v>
+        <v>-1.587301587301</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.027027027027</v>
+        <v>-25.301204819277</v>
       </c>
       <c r="M20" s="15">
-        <v>8</v>
+        <v>10.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.394366197183</v>
+        <v>-91.937581274382</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E21" s="18">
-        <v>16.216216216216</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G21" s="17">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H21" s="18">
-        <v>8.219178082191</v>
+        <v>5.732484076433</v>
       </c>
       <c r="I21" s="17">
-        <v>472</v>
+        <v>517</v>
       </c>
       <c r="J21" s="17">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.278688524590</v>
+        <v>-3.364485981308</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.538720538720</v>
+        <v>-19.21875</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.277432712215</v>
+        <v>0.9765625</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.117756142790</v>
+        <v>-77.763440860215</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
@@ -1207,7 +1207,7 @@
         <v>11.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>11.111111111111</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I23" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J23" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K23" s="15">
-        <v>-13.207547169811</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="M23" s="15">
-        <v>27.777777777777</v>
+        <v>28.947368421052</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E24" s="15">
-        <v>23.684210526315</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="G24" s="14">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H24" s="15">
-        <v>10.824742268041</v>
+        <v>4.838709677419</v>
       </c>
       <c r="I24" s="14">
-        <v>559</v>
+        <v>597</v>
       </c>
       <c r="J24" s="14">
-        <v>564</v>
+        <v>612</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.886524822695</v>
+        <v>-2.450980392156</v>
       </c>
       <c r="L24" s="15">
-        <v>1.636363636363</v>
+        <v>-1.158940397350</v>
       </c>
       <c r="M24" s="15">
-        <v>71.472392638036</v>
+        <v>69.121813031161</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-9.090909090909</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G25" s="14">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.094339622641</v>
+        <v>-14.141414141414</v>
       </c>
       <c r="I25" s="14">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="J25" s="14">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.586206896551</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.661971830985</v>
+        <v>-24.148606811145</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>43.75</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>21.875</v>
+        <v>55.769230769230</v>
       </c>
       <c r="I26" s="14">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="J26" s="14">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K26" s="15">
-        <v>0.980392156862</v>
+        <v>5.164319248826</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.069124423963</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.904761904761</v>
+        <v>0.448430493273</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
+        <v>14</v>
+      </c>
+      <c r="J27" s="14">
         <v>13</v>
       </c>
-      <c r="J27" s="14">
-        <v>11</v>
-      </c>
       <c r="K27" s="15">
-        <v>18.181818181818</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L27" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.315789473684</v>
+        <v>-10</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>300</v>
       </c>
       <c r="L31" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-50</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L15" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M15" s="15">
-        <v>83.333333333333</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.666666666666</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>16.666666666666</v>
+        <v>20.930232558139</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.75</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.974683544303</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.4296875</v>
+        <v>-90.441176470588</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F17" s="14">
+        <v>38</v>
+      </c>
+      <c r="G17" s="14">
         <v>37</v>
       </c>
-      <c r="G17" s="14">
-        <v>39</v>
-      </c>
       <c r="H17" s="15">
-        <v>-5.128205128205</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I17" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="K17" s="15">
-        <v>-25.490196078431</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.490196078431</v>
+        <v>-24.223602484472</v>
       </c>
       <c r="M17" s="15">
-        <v>90</v>
+        <v>87.692307692307</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.237113402061</v>
+        <v>-42.452830188679</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>166.666666666667</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.565217391304</v>
+        <v>-22</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.333333333333</v>
+        <v>-36.065573770491</v>
       </c>
       <c r="M18" s="15">
-        <v>-75</v>
+        <v>-74.509803921568</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.084112149532</v>
+        <v>-93.121693121693</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.263157894736</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F19" s="14">
+        <v>58</v>
+      </c>
+      <c r="G19" s="14">
         <v>67</v>
       </c>
-      <c r="G19" s="14">
-        <v>63</v>
-      </c>
       <c r="H19" s="15">
-        <v>6.349206349206</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="I19" s="14">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="J19" s="14">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="K19" s="15">
-        <v>10.502283105022</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.724409448818</v>
+        <v>-9.025270758122</v>
       </c>
       <c r="M19" s="15">
-        <v>52.201257861635</v>
+        <v>37.704918032786</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.518518518518</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>14.285714285714</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>13.636363636363</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.587301587301</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.301204819277</v>
+        <v>-32.323232323232</v>
       </c>
       <c r="M20" s="15">
-        <v>10.714285714285</v>
+        <v>6.349206349206</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.937581274382</v>
+        <v>-91.748768472906</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="F21" s="17">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G21" s="17">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H21" s="18">
-        <v>5.732484076433</v>
+        <v>0.649350649350</v>
       </c>
       <c r="I21" s="17">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="J21" s="17">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.364485981308</v>
+        <v>-4.537521815008</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.21875</v>
+        <v>-20.839363241678</v>
       </c>
       <c r="M21" s="18">
-        <v>0.9765625</v>
+        <v>-2.146690518783</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.763440860215</v>
+        <v>-77.925746569814</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F23" s="14">
+        <v>17</v>
+      </c>
+      <c r="G23" s="14">
+        <v>14</v>
+      </c>
+      <c r="H23" s="15">
+        <v>21.428571428571</v>
+      </c>
+      <c r="I23" s="14">
+        <v>52</v>
+      </c>
+      <c r="J23" s="14">
+        <v>60</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-13.333333333333</v>
+      </c>
+      <c r="L23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="14">
-        <v>18</v>
-      </c>
-      <c r="G23" s="14">
-        <v>13</v>
-      </c>
-      <c r="H23" s="15">
-        <v>38.461538461538</v>
-      </c>
-      <c r="I23" s="14">
-        <v>49</v>
-      </c>
-      <c r="J23" s="14">
-        <v>56</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-12.5</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-2</v>
-      </c>
       <c r="M23" s="15">
-        <v>28.947368421052</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.833333333333</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="F24" s="14">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G24" s="14">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H24" s="15">
-        <v>4.838709677419</v>
+        <v>-0.520833333333</v>
       </c>
       <c r="I24" s="14">
-        <v>597</v>
+        <v>638</v>
       </c>
       <c r="J24" s="14">
-        <v>612</v>
+        <v>663</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.450980392156</v>
+        <v>-3.770739064856</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.158940397350</v>
+        <v>-0.468018720748</v>
       </c>
       <c r="M24" s="15">
-        <v>69.121813031161</v>
+        <v>63.171355498721</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>-41.666666666666</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F25" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G25" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.141414141414</v>
+        <v>-9.900990099009</v>
       </c>
       <c r="I25" s="14">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="J25" s="14">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.571428571428</v>
+        <v>-28.726287262872</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.148606811145</v>
+        <v>-24.641833810888</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H26" s="15">
-        <v>55.769230769230</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I26" s="14">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="J26" s="14">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="K26" s="15">
-        <v>5.164319248826</v>
+        <v>3.056768558951</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.448275862068</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="M26" s="15">
-        <v>0.448430493273</v>
+        <v>-1.255230125523</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>6</v>
-      </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
         <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>7.692307692307</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L27" s="15">
-        <v>-12.5</v>
+        <v>6.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-10</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N29" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,42 +1538,42 @@
         <v>50</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L31" s="15">
         <v>33.333333333333</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="15">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
-      </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>18.181818181818</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>85.714285714285</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>8.333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>200</v>
+        <v>5</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>36.363636363636</v>
+        <v>62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J16" s="14">
         <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>20.930232558139</v>
+        <v>30.232558139534</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.349397590361</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.095238095238</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.441176470588</v>
+        <v>-90.311418685121</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-36.363636363636</v>
+        <v>70</v>
       </c>
       <c r="F17" s="14">
+        <v>45</v>
+      </c>
+      <c r="G17" s="14">
         <v>38</v>
       </c>
-      <c r="G17" s="14">
-        <v>37</v>
-      </c>
       <c r="H17" s="15">
-        <v>2.702702702702</v>
+        <v>18.421052631578</v>
       </c>
       <c r="I17" s="14">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J17" s="14">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K17" s="15">
-        <v>-25.609756097561</v>
+        <v>-20.114942528735</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.223602484472</v>
+        <v>-18.235294117647</v>
       </c>
       <c r="M17" s="15">
-        <v>87.692307692307</v>
+        <v>95.774647887323</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.452830188679</v>
+        <v>-37.946428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>-22</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.065573770491</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.509803921568</v>
+        <v>-71.875</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.121693121693</v>
+        <v>-92.462311557789</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.666666666666</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.432835820895</v>
+        <v>-17.105263157894</v>
       </c>
       <c r="I19" s="14">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="J19" s="14">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="K19" s="15">
-        <v>7.692307692307</v>
+        <v>5.46875</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.025270758122</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="M19" s="15">
-        <v>37.704918032786</v>
+        <v>33.663366336633</v>
       </c>
       <c r="N19" s="15">
-        <v>-22.222222222222</v>
+        <v>-20.588235294117</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>30.434782608695</v>
       </c>
       <c r="I20" s="14">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J20" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.285714285714</v>
+        <v>6.756756756756</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.323232323232</v>
+        <v>-24.038461538461</v>
       </c>
       <c r="M20" s="15">
-        <v>6.349206349206</v>
+        <v>17.910447761194</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.748768472906</v>
+        <v>-90.867052023121</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.421052631578</v>
+        <v>46.341463414634</v>
       </c>
       <c r="F21" s="17">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G21" s="17">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H21" s="18">
-        <v>0.649350649350</v>
+        <v>7.975460122699</v>
       </c>
       <c r="I21" s="17">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="J21" s="17">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.537521815008</v>
+        <v>-1.302931596091</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.839363241678</v>
+        <v>-17.551020408163</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.146690518783</v>
+        <v>1.168614357262</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.925746569814</v>
+        <v>-76.896683187190</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
         <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>21.428571428571</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I23" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J23" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K23" s="15">
-        <v>-13.333333333333</v>
+        <v>-10.769230769230</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>5.454545454545</v>
       </c>
       <c r="M23" s="15">
-        <v>33.333333333333</v>
+        <v>48.717948717948</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.686274509803</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="G24" s="14">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.520833333333</v>
+        <v>-12.154696132596</v>
       </c>
       <c r="I24" s="14">
-        <v>638</v>
+        <v>672</v>
       </c>
       <c r="J24" s="14">
-        <v>663</v>
+        <v>707</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.770739064856</v>
+        <v>-4.950495049504</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.468018720748</v>
+        <v>-0.884955752212</v>
       </c>
       <c r="M24" s="15">
-        <v>63.171355498721</v>
+        <v>57.746478873239</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-26.923076923076</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H25" s="15">
-        <v>-9.900990099009</v>
+        <v>-32.978723404255</v>
       </c>
       <c r="I25" s="14">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="J25" s="14">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.726287262872</v>
+        <v>-29.923273657289</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.641833810888</v>
+        <v>-25.945945945945</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G26" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>36.842105263157</v>
+        <v>32.758620689655</v>
       </c>
       <c r="I26" s="14">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="J26" s="14">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="K26" s="15">
-        <v>3.056768558951</v>
+        <v>5.284552845528</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.349206349206</v>
+        <v>-4.074074074074</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.255230125523</v>
+        <v>2.371541501976</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>30.769230769230</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L27" s="15">
-        <v>6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.761904761904</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N29" s="15">
         <v>-75</v>
@@ -1538,7 +1538,7 @@
         <v>50</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
         <v>-75</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M15" s="15">
-        <v>114.285714285714</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -943,31 +943,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>62.5</v>
+        <v>366.666666666667</v>
       </c>
       <c r="I16" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J16" s="14">
         <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>30.232558139534</v>
+        <v>37.209302325581</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.130434782608</v>
+        <v>-41</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.363636363636</v>
+        <v>-37.234042553191</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.311418685121</v>
+        <v>-90.296052631578</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15">
-        <v>70</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F17" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>18.421052631578</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J17" s="14">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="K17" s="15">
-        <v>-20.114942528735</v>
+        <v>-22.797927461139</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.235294117647</v>
+        <v>-17.679558011049</v>
       </c>
       <c r="M17" s="15">
-        <v>95.774647887323</v>
+        <v>88.607594936708</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.946428571428</v>
+        <v>-37.130801687763</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
         <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>58.333333333333</v>
+        <v>18.75</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.769230769230</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M18" s="15">
-        <v>-71.875</v>
+        <v>-70.370370370370</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.462311557789</v>
+        <v>-92.405063291139</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.105263157894</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="I19" s="14">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="J19" s="14">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="K19" s="15">
-        <v>5.46875</v>
+        <v>5.166051660516</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.163265306122</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="M19" s="15">
-        <v>33.663366336633</v>
+        <v>35.071090047393</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.588235294117</v>
+        <v>-20.168067226890</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F20" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G20" s="14">
         <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>30.434782608695</v>
+        <v>52.173913043478</v>
       </c>
       <c r="I20" s="14">
+        <v>88</v>
+      </c>
+      <c r="J20" s="14">
         <v>79</v>
       </c>
-      <c r="J20" s="14">
-        <v>74</v>
-      </c>
       <c r="K20" s="15">
-        <v>6.756756756756</v>
+        <v>11.392405063291</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.038461538461</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>17.910447761194</v>
+        <v>18.918918918918</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.867052023121</v>
+        <v>-90.276243093922</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>46.341463414634</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H21" s="18">
-        <v>7.975460122699</v>
+        <v>3.508771929824</v>
       </c>
       <c r="I21" s="17">
-        <v>606</v>
+        <v>647</v>
       </c>
       <c r="J21" s="17">
-        <v>614</v>
+        <v>659</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.302931596091</v>
+        <v>-1.820940819423</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.551020408163</v>
+        <v>-16.731016731016</v>
       </c>
       <c r="M21" s="18">
-        <v>1.168614357262</v>
+        <v>2.535657686212</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.896683187190</v>
+        <v>-76.540971718636</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>28.571428571428</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J23" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K23" s="15">
-        <v>-10.769230769230</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L23" s="15">
-        <v>5.454545454545</v>
+        <v>1.694915254237</v>
       </c>
       <c r="M23" s="15">
-        <v>48.717948717948</v>
+        <v>39.534883720930</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="G24" s="14">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.154696132596</v>
+        <v>-21.989528795811</v>
       </c>
       <c r="I24" s="14">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="J24" s="14">
-        <v>707</v>
+        <v>755</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.950495049504</v>
+        <v>-6.092715231788</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.884955752212</v>
+        <v>-0.421348314606</v>
       </c>
       <c r="M24" s="15">
-        <v>57.746478873239</v>
+        <v>53.463203463203</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="F25" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.978723404255</v>
+        <v>-37.373737373737</v>
       </c>
       <c r="I25" s="14">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="J25" s="14">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.923273657289</v>
+        <v>-29.904306220095</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.945945945945</v>
+        <v>-23.697916666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>35.294117647058</v>
+        <v>30</v>
       </c>
       <c r="F26" s="14">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>32.758620689655</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I26" s="14">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="J26" s="14">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="K26" s="15">
-        <v>5.284552845528</v>
+        <v>5.859375</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.074074074074</v>
+        <v>-4.577464788732</v>
       </c>
       <c r="M26" s="15">
-        <v>2.371541501976</v>
+        <v>1.119402985074</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>35.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>11.764705882352</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>125</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>4.545454545454</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>15</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,35 +1469,35 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
         <v>-75</v>
@@ -1510,35 +1510,35 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L30" s="15">
         <v>50</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
         <v>-75</v>
@@ -1558,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -905,28 +905,28 @@
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>45.454545454545</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M15" s="15">
-        <v>128.571428571429</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N15" s="15">
-        <v>33.333333333333</v>
+        <v>13.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="D16" s="14">
+        <v>6</v>
+      </c>
+      <c r="E16" s="15">
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>366.666666666667</v>
+        <v>142.857142857143</v>
       </c>
       <c r="I16" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>37.209302325581</v>
+        <v>34.693877551020</v>
       </c>
       <c r="L16" s="15">
-        <v>-41</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.234042553191</v>
+        <v>-34</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.296052631578</v>
+        <v>-89.622641509434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.105263157894</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F17" s="14">
         <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="I17" s="14">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="J17" s="14">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="K17" s="15">
-        <v>-22.797927461139</v>
+        <v>-24.271844660194</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.679558011049</v>
+        <v>-17.460317460317</v>
       </c>
       <c r="M17" s="15">
-        <v>88.607594936708</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.130801687763</v>
+        <v>-39.0625</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
         <v>19</v>
       </c>
-      <c r="G18" s="14">
-        <v>16</v>
-      </c>
       <c r="H18" s="15">
-        <v>18.75</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.644067796610</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="L18" s="15">
-        <v>-29.411764705882</v>
+        <v>-32.876712328767</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.370370370370</v>
+        <v>-71.176470588235</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.405063291139</v>
+        <v>-92.653673163418</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>13.333333333333</v>
+        <v>-35</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.084507042253</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="J19" s="14">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="K19" s="15">
-        <v>5.166051660516</v>
+        <v>3.092783505154</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.557377049180</v>
+        <v>-7.120743034055</v>
       </c>
       <c r="M19" s="15">
-        <v>35.071090047393</v>
+        <v>35.135135135135</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.168067226890</v>
+        <v>-19.354838709677</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>52.173913043478</v>
+        <v>55</v>
       </c>
       <c r="I20" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J20" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K20" s="15">
-        <v>11.392405063291</v>
+        <v>10.843373493975</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.428571428571</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>18.918918918918</v>
+        <v>12.195121951219</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.276243093922</v>
+        <v>-90.376569037656</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.444444444444</v>
+        <v>-28</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G21" s="17">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H21" s="18">
-        <v>3.508771929824</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I21" s="17">
-        <v>647</v>
+        <v>682</v>
       </c>
       <c r="J21" s="17">
-        <v>659</v>
+        <v>709</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.820940819423</v>
+        <v>-3.808180535966</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.731016731016</v>
+        <v>-17.031630170316</v>
       </c>
       <c r="M21" s="18">
-        <v>2.535657686212</v>
+        <v>1.943198804185</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.540971718636</v>
+        <v>-76.555517359917</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-6.666666666666</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I23" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.764705882352</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="L23" s="15">
-        <v>1.694915254237</v>
+        <v>3.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>39.534883720930</v>
+        <v>55.813953488372</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.916666666666</v>
+        <v>21.212121212121</v>
       </c>
       <c r="F24" s="14">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G24" s="14">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.989528795811</v>
+        <v>-13.068181818181</v>
       </c>
       <c r="I24" s="14">
-        <v>709</v>
+        <v>749</v>
       </c>
       <c r="J24" s="14">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.092715231788</v>
+        <v>-4.949238578680</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.421348314606</v>
+        <v>-1.187335092348</v>
       </c>
       <c r="M24" s="15">
-        <v>53.463203463203</v>
+        <v>51.313131313131</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.629629629629</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F25" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G25" s="14">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.373737373737</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I25" s="14">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="J25" s="14">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.904306220095</v>
+        <v>-29.195402298850</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.697916666666</v>
+        <v>-25.242718446601</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>30</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>26.923076923076</v>
+        <v>14.754098360655</v>
       </c>
       <c r="I26" s="14">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="J26" s="14">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="K26" s="15">
-        <v>5.859375</v>
+        <v>6.934306569343</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.577464788732</v>
+        <v>-5.177993527508</v>
       </c>
       <c r="M26" s="15">
-        <v>1.119402985074</v>
+        <v>1.384083044982</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>75</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="L27" s="15">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.111111111111</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>33.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-114pct.xlsx
+++ b/data/source/weekly/cs-en-us-114pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -885,7 +885,7 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,31 +902,31 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>54.545454545454</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M15" s="15">
-        <v>142.857142857143</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>13.333333333333</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>142.857142857143</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>34.693877551020</v>
+        <v>30.909090909090</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.735849056603</v>
+        <v>-37.391304347826</v>
       </c>
       <c r="M16" s="15">
-        <v>-34</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.622641509434</v>
+        <v>-89.205397301349</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-38.461538461538</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.754716981132</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J17" s="14">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="K17" s="15">
-        <v>-24.271844660194</v>
+        <v>-23.584905660377</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.460317460317</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>85.714285714285</v>
+        <v>86.206896551724</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.0625</v>
+        <v>-41.935483870967</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
+        <v>-39.130434782608</v>
+      </c>
+      <c r="I18" s="14">
+        <v>52</v>
+      </c>
+      <c r="J18" s="14">
+        <v>73</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-28.767123287671</v>
+      </c>
+      <c r="L18" s="15">
         <v>-31.578947368421</v>
       </c>
-      <c r="I18" s="14">
-        <v>49</v>
-      </c>
-      <c r="J18" s="14">
-        <v>65</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-24.615384615384</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-32.876712328767</v>
-      </c>
       <c r="M18" s="15">
-        <v>-71.176470588235</v>
+        <v>-70.454545454545</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.653673163418</v>
+        <v>-92.737430167597</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>-35</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.055555555555</v>
+        <v>-32.941176470588</v>
       </c>
       <c r="I19" s="14">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="J19" s="14">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="K19" s="15">
-        <v>3.092783505154</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.120743034055</v>
+        <v>-11.239193083573</v>
       </c>
       <c r="M19" s="15">
-        <v>35.135135135135</v>
+        <v>31.063829787234</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.354838709677</v>
+        <v>-21.428571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>16</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
       <c r="E20" s="15">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>55</v>
+        <v>127.777777777778</v>
       </c>
       <c r="I20" s="14">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J20" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K20" s="15">
-        <v>10.843373493975</v>
+        <v>22.727272727272</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.333333333333</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M20" s="15">
-        <v>12.195121951219</v>
+        <v>25.581395348837</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.376569037656</v>
+        <v>-89.232303090727</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-28</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.448275862068</v>
+        <v>-6.282722513089</v>
       </c>
       <c r="I21" s="17">
-        <v>682</v>
+        <v>722</v>
       </c>
       <c r="J21" s="17">
-        <v>709</v>
+        <v>764</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.808180535966</v>
+        <v>-5.497382198952</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.031630170316</v>
+        <v>-16.820276497695</v>
       </c>
       <c r="M21" s="18">
-        <v>1.943198804185</v>
+        <v>3.142857142857</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.555517359917</v>
+        <v>-76.581252027246</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L22" s="15">
         <v>33.333333333333</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>5.882352941176</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J23" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K23" s="15">
-        <v>-8.219178082191</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="L23" s="15">
-        <v>3.076923076923</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="M23" s="15">
-        <v>55.813953488372</v>
+        <v>47.826086956521</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E24" s="15">
-        <v>21.212121212121</v>
+        <v>2.272727272727</v>
       </c>
       <c r="F24" s="14">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G24" s="14">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.068181818181</v>
+        <v>-10.059171597633</v>
       </c>
       <c r="I24" s="14">
-        <v>749</v>
+        <v>790</v>
       </c>
       <c r="J24" s="14">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.949238578680</v>
+        <v>-5.048076923076</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.187335092348</v>
+        <v>-1.618929016189</v>
       </c>
       <c r="M24" s="15">
-        <v>51.313131313131</v>
+        <v>53.996101364522</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>-17.647058823529</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F25" s="14">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G25" s="14">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H25" s="15">
-        <v>-30.434782608695</v>
+        <v>-34.831460674157</v>
       </c>
       <c r="I25" s="14">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="J25" s="14">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.195402298850</v>
+        <v>-29.912663755458</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.242718446601</v>
+        <v>-25.866050808314</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>14.754098360655</v>
+        <v>21.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="J26" s="14">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="K26" s="15">
-        <v>6.934306569343</v>
+        <v>6.920415224913</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.177993527508</v>
+        <v>-6.646525679758</v>
       </c>
       <c r="M26" s="15">
-        <v>1.384083044982</v>
+        <v>-1.277955271565</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="14">
-        <v>7</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
-      <c r="H27" s="15">
-        <v>133.333333333333</v>
-      </c>
       <c r="I27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>31.25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>66.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
+        <v>10</v>
+      </c>
+      <c r="G28" s="14">
         <v>11</v>
       </c>
-      <c r="G28" s="14">
-        <v>9</v>
-      </c>
       <c r="H28" s="15">
-        <v>22.222222222222</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>7.407407407407</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.923076923076</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.923076923076</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>3</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>50</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>7</v>
